--- a/importer/live/standings/Player-Rankings-TznNqHP1zjSPHUOSSnko.xlsx
+++ b/importer/live/standings/Player-Rankings-TznNqHP1zjSPHUOSSnko.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/E914DC20F5C50B12/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C33CA6E8-F671-49C6-BD31-326B9A39E868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3276126-065C-413E-9D0D-4C87188C0690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6AF0296B-6045-4659-8676-3A12C91545FD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FFEB52E2-367C-4193-8300-5A5BCC80BCB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Player-Rankings-TznNqHP1zjSPHUO" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="57">
   <si>
     <t>Rank</t>
   </si>
@@ -64,66 +64,90 @@
     <t>Kevin Monahan</t>
   </si>
   <si>
+    <t>Michael Crews</t>
+  </si>
+  <si>
+    <t>Charles Maione</t>
+  </si>
+  <si>
+    <t>PxP PC</t>
+  </si>
+  <si>
     <t>Tony Romano</t>
   </si>
   <si>
     <t>Club Name Not Set</t>
   </si>
   <si>
-    <t>Charles Maione</t>
-  </si>
-  <si>
-    <t>PxP PC</t>
+    <t>Frank Rossetti</t>
+  </si>
+  <si>
+    <t>Martha Garzon</t>
+  </si>
+  <si>
+    <t>Brendan Stephenson</t>
+  </si>
+  <si>
+    <t>Jeff Thompson</t>
   </si>
   <si>
     <t>Renata Pisani</t>
   </si>
   <si>
-    <t>Michael Crews</t>
-  </si>
-  <si>
     <t>Sal Farruggia</t>
   </si>
   <si>
     <t>LI-Kick</t>
   </si>
   <si>
-    <t>Martha Garzon</t>
-  </si>
-  <si>
     <t>Andrew Johnson</t>
   </si>
   <si>
-    <t>Frank Rossetti</t>
-  </si>
-  <si>
-    <t>Brendan Stephenson</t>
-  </si>
-  <si>
-    <t>Jeff Thompson</t>
+    <t>Daniel Calhoun</t>
+  </si>
+  <si>
+    <t>Val Kats</t>
+  </si>
+  <si>
+    <t>Hiro Fujiwara</t>
+  </si>
+  <si>
+    <t>Cecilia Jozef</t>
+  </si>
+  <si>
+    <t>Stephen Rizzi</t>
   </si>
   <si>
     <t>Jason Vargas</t>
   </si>
   <si>
+    <t>Gino Schettini</t>
+  </si>
+  <si>
+    <t>Eddie Rizzi</t>
+  </si>
+  <si>
     <t>Arthur Galo</t>
   </si>
   <si>
     <t>1 Pickleball Plaza</t>
   </si>
   <si>
-    <t>Daniel Calhoun</t>
+    <t>Heidi Callahan</t>
   </si>
   <si>
     <t>Lauren Glodny</t>
   </si>
   <si>
-    <t>Hiro Fujiwara</t>
-  </si>
-  <si>
     <t>Jay Colapinto</t>
   </si>
   <si>
+    <t>Erik Deangelis</t>
+  </si>
+  <si>
+    <t>Vic Daddario</t>
+  </si>
+  <si>
     <t>Jeff Fein</t>
   </si>
   <si>
@@ -133,9 +157,6 @@
     <t>Keri Feng</t>
   </si>
   <si>
-    <t>Val Kats</t>
-  </si>
-  <si>
     <t>Gms</t>
   </si>
   <si>
@@ -154,7 +175,7 @@
     <t>Pts for</t>
   </si>
   <si>
-    <t>Pts aga</t>
+    <t>pts aga</t>
   </si>
   <si>
     <t>Diff</t>
@@ -166,7 +187,7 @@
     <t>TUESDAY AM</t>
   </si>
   <si>
-    <t>WEEK 6</t>
+    <t>9 WEEKS</t>
   </si>
   <si>
     <t>MERRICK IN A PICKLE</t>
@@ -179,7 +200,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -315,13 +336,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="18"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Lucida Handwriting"/>
-      <family val="4"/>
+      <name val="Grandview"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="ADLaM Display"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -515,13 +541,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -701,7 +751,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -712,13 +762,10 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -727,22 +774,39 @@
     <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="38" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1117,120 +1181,134 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4463BA-C098-44EC-AB39-2662E8AB4DDF}">
-  <dimension ref="A1:P27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F22184EF-E7D9-49E4-BAD4-A7F322EC31CF}">
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="19" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="14" customFormat="1" ht="24.75" x14ac:dyDescent="0.45">
-      <c r="B1" s="14" t="s">
+    <row r="1" spans="1:16" s="15" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18"/>
+      <c r="B1" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+    </row>
+    <row r="2" spans="1:16" s="17" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="K2" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L2" s="16" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>46</v>
+      <c r="M2" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="O2" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="P2" s="16" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="6">
-        <v>83</v>
-      </c>
-      <c r="E3" s="6">
-        <v>34</v>
+      <c r="D3" s="4">
+        <v>124</v>
+      </c>
+      <c r="E3" s="4">
+        <v>53</v>
       </c>
       <c r="F3" s="1">
-        <v>30</v>
-      </c>
-      <c r="G3" s="6">
-        <v>64</v>
+        <v>44</v>
+      </c>
+      <c r="G3" s="4">
+        <v>97</v>
       </c>
       <c r="H3" s="2">
-        <v>0.53100000000000003</v>
-      </c>
-      <c r="I3" s="6">
-        <v>6</v>
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="I3" s="4">
+        <v>9</v>
       </c>
       <c r="J3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>4</v>
-      </c>
-      <c r="L3" s="7">
+        <v>3</v>
+      </c>
+      <c r="L3" s="6">
         <f>D3/I3</f>
-        <v>13.833333333333334</v>
-      </c>
-      <c r="M3" s="1">
-        <v>637</v>
+        <v>13.777777777777779</v>
+      </c>
+      <c r="M3" s="4">
+        <v>971</v>
       </c>
       <c r="N3" s="1">
-        <v>613</v>
+        <v>934</v>
       </c>
       <c r="O3" s="1">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="P3" s="1"/>
     </row>
@@ -1238,101 +1316,101 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="8">
-        <v>82</v>
-      </c>
-      <c r="E4" s="8">
-        <v>32</v>
+      <c r="D4" s="7">
+        <v>120</v>
+      </c>
+      <c r="E4" s="7">
+        <v>49</v>
       </c>
       <c r="F4" s="1">
-        <v>20</v>
-      </c>
-      <c r="G4" s="13">
-        <v>52</v>
+        <v>24</v>
+      </c>
+      <c r="G4" s="1">
+        <v>73</v>
       </c>
       <c r="H4" s="2">
-        <v>0.61499999999999999</v>
-      </c>
-      <c r="I4" s="8">
-        <v>5</v>
-      </c>
-      <c r="J4" s="6">
-        <v>4</v>
+        <v>0.67100000000000004</v>
+      </c>
+      <c r="I4" s="1">
+        <v>7</v>
+      </c>
+      <c r="J4" s="4">
+        <v>6</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
       </c>
-      <c r="L4" s="7">
-        <f t="shared" ref="L4:L27" si="0">D4/I4</f>
-        <v>16.399999999999999</v>
-      </c>
-      <c r="M4" s="1">
-        <v>532</v>
+      <c r="L4" s="6">
+        <f t="shared" ref="L4:L34" si="0">D4/I4</f>
+        <v>17.142857142857142</v>
+      </c>
+      <c r="M4" s="14">
+        <v>765</v>
       </c>
       <c r="N4" s="1">
-        <v>480</v>
-      </c>
-      <c r="O4" s="11">
-        <v>52</v>
-      </c>
-      <c r="P4" s="8">
-        <v>1</v>
+        <v>645</v>
+      </c>
+      <c r="O4" s="4">
+        <v>120</v>
+      </c>
+      <c r="P4" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="11">
-        <v>68</v>
-      </c>
-      <c r="E5" s="11">
-        <v>28</v>
+      <c r="D5" s="12">
+        <v>109</v>
+      </c>
+      <c r="E5" s="12">
+        <v>44</v>
       </c>
       <c r="F5" s="1">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G5" s="1">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="H5" s="2">
-        <v>0.68300000000000005</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="I5" s="1">
+        <v>7</v>
+      </c>
+      <c r="J5" s="7">
         <v>4</v>
       </c>
-      <c r="J5" s="8">
-        <v>3</v>
-      </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
-      <c r="L5" s="12">
-        <f t="shared" si="0"/>
-        <v>17</v>
+      <c r="L5" s="6">
+        <f t="shared" si="0"/>
+        <v>15.571428571428571</v>
       </c>
       <c r="M5" s="1">
-        <v>417</v>
+        <v>724</v>
       </c>
       <c r="N5" s="1">
-        <v>356</v>
-      </c>
-      <c r="O5" s="8">
-        <v>61</v>
-      </c>
-      <c r="P5" s="8">
+        <v>653</v>
+      </c>
+      <c r="O5" s="13">
+        <v>71</v>
+      </c>
+      <c r="P5" s="1">
         <v>1</v>
       </c>
     </row>
@@ -1347,22 +1425,22 @@
         <v>8</v>
       </c>
       <c r="D6" s="1">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="E6" s="1">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F6" s="1">
-        <v>30</v>
-      </c>
-      <c r="G6" s="8">
-        <v>54</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0.44400000000000001</v>
-      </c>
-      <c r="I6" s="8">
-        <v>5</v>
+        <v>47</v>
+      </c>
+      <c r="G6" s="7">
+        <v>87</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="I6" s="7">
+        <v>8</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
@@ -1370,18 +1448,18 @@
       <c r="K6" s="1">
         <v>4</v>
       </c>
-      <c r="L6" s="7">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="M6" s="1">
-        <v>532</v>
+      <c r="L6" s="6">
+        <f t="shared" si="0"/>
+        <v>12.875</v>
+      </c>
+      <c r="M6" s="7">
+        <v>836</v>
       </c>
       <c r="N6" s="1">
-        <v>537</v>
+        <v>842</v>
       </c>
       <c r="O6" s="1">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="P6" s="1"/>
     </row>
@@ -1396,44 +1474,44 @@
         <v>8</v>
       </c>
       <c r="D7" s="1">
-        <v>62</v>
-      </c>
-      <c r="E7" s="1">
-        <v>25</v>
+        <v>102</v>
+      </c>
+      <c r="E7" s="12">
+        <v>44</v>
       </c>
       <c r="F7" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="H7" s="2">
-        <v>0.625</v>
+        <v>0.72099999999999997</v>
       </c>
       <c r="I7" s="1">
+        <v>6</v>
+      </c>
+      <c r="J7" s="7">
         <v>4</v>
       </c>
-      <c r="J7" s="11">
-        <v>2</v>
-      </c>
       <c r="K7" s="1">
         <v>1</v>
       </c>
-      <c r="L7" s="7">
-        <f t="shared" si="0"/>
-        <v>15.5</v>
+      <c r="L7" s="11">
+        <f t="shared" si="0"/>
+        <v>17</v>
       </c>
       <c r="M7" s="1">
-        <v>411</v>
+        <v>640</v>
       </c>
       <c r="N7" s="1">
-        <v>388</v>
-      </c>
-      <c r="O7" s="1">
-        <v>23</v>
-      </c>
-      <c r="P7" s="8">
-        <v>1</v>
+        <v>540</v>
+      </c>
+      <c r="O7" s="7">
+        <v>100</v>
+      </c>
+      <c r="P7" s="4">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -1444,44 +1522,44 @@
         <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D8" s="1">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="E8" s="1">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F8" s="1">
-        <v>18</v>
-      </c>
-      <c r="G8" s="1">
-        <v>43</v>
+        <v>52</v>
+      </c>
+      <c r="G8" s="12">
+        <v>81</v>
       </c>
       <c r="H8" s="2">
-        <v>0.58099999999999996</v>
-      </c>
-      <c r="I8" s="1">
+        <v>0.35799999999999998</v>
+      </c>
+      <c r="I8" s="7">
+        <v>8</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
         <v>4</v>
       </c>
-      <c r="J8" s="1">
-        <v>1</v>
-      </c>
-      <c r="K8" s="1">
-        <v>2</v>
-      </c>
-      <c r="L8" s="7">
-        <f t="shared" si="0"/>
-        <v>14.5</v>
+      <c r="L8" s="6">
+        <f t="shared" si="0"/>
+        <v>9.875</v>
       </c>
       <c r="M8" s="1">
-        <v>448</v>
+        <v>733</v>
       </c>
       <c r="N8" s="1">
-        <v>409</v>
+        <v>840</v>
       </c>
       <c r="O8" s="1">
-        <v>39</v>
+        <v>-107</v>
       </c>
       <c r="P8" s="1"/>
     </row>
@@ -1490,28 +1568,28 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="D9" s="1">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="E9" s="1">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F9" s="1">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G9" s="1">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="H9" s="2">
-        <v>0.432</v>
+        <v>0.40899999999999997</v>
       </c>
       <c r="I9" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J9" s="1">
         <v>1</v>
@@ -1519,18 +1597,18 @@
       <c r="K9" s="1">
         <v>3</v>
       </c>
-      <c r="L9" s="7">
-        <f t="shared" si="0"/>
-        <v>12</v>
+      <c r="L9" s="6">
+        <f t="shared" si="0"/>
+        <v>11.333333333333334</v>
       </c>
       <c r="M9" s="1">
-        <v>408</v>
+        <v>605</v>
       </c>
       <c r="N9" s="1">
-        <v>446</v>
+        <v>675</v>
       </c>
       <c r="O9" s="1">
-        <v>-38</v>
+        <v>-70</v>
       </c>
       <c r="P9" s="1"/>
     </row>
@@ -1539,28 +1617,28 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="D10" s="1">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E10" s="1">
+        <v>25</v>
+      </c>
+      <c r="F10" s="1">
         <v>18</v>
       </c>
-      <c r="F10" s="1">
-        <v>12</v>
-      </c>
       <c r="G10" s="1">
-        <v>30</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0.6</v>
+        <v>43</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.58099999999999996</v>
       </c>
       <c r="I10" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" s="1">
         <v>1</v>
@@ -1568,24 +1646,24 @@
       <c r="K10" s="1">
         <v>2</v>
       </c>
-      <c r="L10" s="7">
-        <f t="shared" si="0"/>
-        <v>14.666666666666666</v>
+      <c r="L10" s="6">
+        <f t="shared" si="0"/>
+        <v>14.5</v>
       </c>
       <c r="M10" s="1">
-        <v>309</v>
+        <v>448</v>
       </c>
       <c r="N10" s="1">
-        <v>292</v>
+        <v>409</v>
       </c>
       <c r="O10" s="1">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>19</v>
@@ -1594,41 +1672,41 @@
         <v>8</v>
       </c>
       <c r="D11" s="1">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E11" s="1">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F11" s="1">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G11" s="1">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H11" s="2">
-        <v>0.29199999999999998</v>
-      </c>
-      <c r="I11" s="8">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="I11" s="1">
         <v>5</v>
       </c>
       <c r="J11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>9</v>
-      </c>
-      <c r="L11" s="7">
-        <f t="shared" si="0"/>
-        <v>8.8000000000000007</v>
+        <v>3</v>
+      </c>
+      <c r="L11" s="6">
+        <f t="shared" si="0"/>
+        <v>11.2</v>
       </c>
       <c r="M11" s="1">
-        <v>424</v>
+        <v>514</v>
       </c>
       <c r="N11" s="1">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="O11" s="1">
-        <v>-93</v>
+        <v>-23</v>
       </c>
       <c r="P11" s="1"/>
     </row>
@@ -1640,144 +1718,144 @@
         <v>20</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D12" s="1">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E12" s="1">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F12" s="1">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="G12" s="1">
-        <v>25</v>
-      </c>
-      <c r="H12" s="3">
-        <v>0.8</v>
+        <v>66</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.19700000000000001</v>
       </c>
       <c r="I12" s="1">
-        <v>2</v>
-      </c>
-      <c r="J12" s="11">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>1</v>
-      </c>
-      <c r="L12" s="9">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <v>8</v>
+      </c>
+      <c r="L12" s="6">
+        <f t="shared" si="0"/>
+        <v>8.8333333333333339</v>
       </c>
       <c r="M12" s="1">
-        <v>270</v>
+        <v>517</v>
       </c>
       <c r="N12" s="1">
-        <v>208</v>
-      </c>
-      <c r="O12" s="6">
-        <v>62</v>
-      </c>
-      <c r="P12" s="6">
-        <v>2</v>
-      </c>
+        <v>688</v>
+      </c>
+      <c r="O12" s="1">
+        <v>-171</v>
+      </c>
+      <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="1">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E13" s="1">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F13" s="1">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H13" s="2">
-        <v>0.24399999999999999</v>
+        <v>0.63600000000000001</v>
       </c>
       <c r="I13" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>8</v>
-      </c>
-      <c r="L13" s="7">
-        <f t="shared" si="0"/>
-        <v>9.75</v>
+        <v>1</v>
+      </c>
+      <c r="L13" s="6">
+        <f t="shared" si="0"/>
+        <v>16.333333333333332</v>
       </c>
       <c r="M13" s="1">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="N13" s="1">
-        <v>458</v>
+        <v>270</v>
       </c>
       <c r="O13" s="1">
-        <v>-97</v>
-      </c>
-      <c r="P13" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="P13" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1">
+        <v>47</v>
+      </c>
+      <c r="E14" s="1">
+        <v>21</v>
+      </c>
+      <c r="F14" s="1">
         <v>11</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="1">
-        <v>39</v>
-      </c>
-      <c r="E14" s="1">
-        <v>17</v>
-      </c>
-      <c r="F14" s="1">
-        <v>18</v>
-      </c>
       <c r="G14" s="1">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H14" s="2">
-        <v>0.48599999999999999</v>
+        <v>0.65600000000000003</v>
       </c>
       <c r="I14" s="1">
         <v>3</v>
       </c>
       <c r="J14" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" s="1">
-        <v>4</v>
-      </c>
-      <c r="L14" s="7">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="L14" s="6">
+        <f t="shared" si="0"/>
+        <v>15.666666666666666</v>
       </c>
       <c r="M14" s="1">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="N14" s="1">
-        <v>336</v>
+        <v>287</v>
       </c>
       <c r="O14" s="1">
-        <v>-13</v>
+        <v>32</v>
       </c>
       <c r="P14" s="1"/>
     </row>
@@ -1786,25 +1864,25 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="1">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E15" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F15" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G15" s="1">
-        <v>34</v>
-      </c>
-      <c r="H15" s="2">
-        <v>0.441</v>
+        <v>30</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.6</v>
       </c>
       <c r="I15" s="1">
         <v>3</v>
@@ -1813,20 +1891,20 @@
         <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>3</v>
-      </c>
-      <c r="L15" s="7">
-        <f t="shared" si="0"/>
-        <v>11.666666666666666</v>
+        <v>2</v>
+      </c>
+      <c r="L15" s="6">
+        <f t="shared" si="0"/>
+        <v>14.666666666666666</v>
       </c>
       <c r="M15" s="1">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="N15" s="1">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="O15" s="1">
-        <v>-6</v>
+        <v>17</v>
       </c>
       <c r="P15" s="1"/>
     </row>
@@ -1835,50 +1913,50 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="D16" s="1">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E16" s="1">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F16" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1">
-        <v>22</v>
-      </c>
-      <c r="H16" s="2">
-        <v>0.63600000000000001</v>
+        <v>25</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0.8</v>
       </c>
       <c r="I16" s="1">
         <v>2</v>
       </c>
       <c r="J16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" s="1">
         <v>1</v>
       </c>
-      <c r="L16" s="7">
-        <f t="shared" si="0"/>
-        <v>17</v>
+      <c r="L16" s="9">
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="M16" s="1">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="N16" s="1">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="O16" s="1">
-        <v>37</v>
-      </c>
-      <c r="P16" s="8">
-        <v>1</v>
+        <v>62</v>
+      </c>
+      <c r="P16" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -1892,41 +1970,41 @@
         <v>8</v>
       </c>
       <c r="D17" s="1">
+        <v>39</v>
+      </c>
+      <c r="E17" s="1">
+        <v>17</v>
+      </c>
+      <c r="F17" s="1">
         <v>18</v>
       </c>
-      <c r="E17" s="1">
-        <v>7</v>
-      </c>
-      <c r="F17" s="1">
+      <c r="G17" s="1">
+        <v>35</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="I17" s="1">
         <v>3</v>
       </c>
-      <c r="G17" s="1">
-        <v>10</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="I17" s="1">
-        <v>1</v>
-      </c>
       <c r="J17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>2</v>
-      </c>
-      <c r="L17" s="10">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <v>4</v>
+      </c>
+      <c r="L17" s="6">
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="M17" s="1">
-        <v>103</v>
+        <v>323</v>
       </c>
       <c r="N17" s="1">
-        <v>93</v>
+        <v>336</v>
       </c>
       <c r="O17" s="1">
-        <v>10</v>
+        <v>-13</v>
       </c>
       <c r="P17" s="1"/>
     </row>
@@ -1941,41 +2019,41 @@
         <v>8</v>
       </c>
       <c r="D18" s="1">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E18" s="1">
+        <v>10</v>
+      </c>
+      <c r="F18" s="1">
+        <v>9</v>
+      </c>
+      <c r="G18" s="1">
+        <v>19</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0.52600000000000002</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
         <v>6</v>
       </c>
-      <c r="F18" s="1">
-        <v>4</v>
-      </c>
-      <c r="G18" s="1">
-        <v>10</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="I18" s="1">
-        <v>1</v>
-      </c>
-      <c r="J18" s="1">
-        <v>1</v>
-      </c>
-      <c r="K18" s="1">
-        <v>3</v>
-      </c>
-      <c r="L18" s="7">
-        <f t="shared" si="0"/>
-        <v>16</v>
+      <c r="L18" s="6">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
       </c>
       <c r="M18" s="1">
-        <v>105</v>
+        <v>184</v>
       </c>
       <c r="N18" s="1">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="O18" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P18" s="1"/>
     </row>
@@ -1987,93 +2065,93 @@
         <v>28</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D19" s="1">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E19" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G19" s="1">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="H19" s="2">
-        <v>0.54500000000000004</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="I19" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J19" s="1">
         <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>6</v>
-      </c>
-      <c r="L19" s="7">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="L19" s="6">
+        <f t="shared" si="0"/>
+        <v>7.333333333333333</v>
       </c>
       <c r="M19" s="1">
-        <v>104</v>
+        <v>256</v>
       </c>
       <c r="N19" s="1">
-        <v>91</v>
+        <v>355</v>
       </c>
       <c r="O19" s="1">
-        <v>13</v>
+        <v>-99</v>
       </c>
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="1">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E20" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F20" s="1">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G20" s="1">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H20" s="2">
-        <v>0.55600000000000005</v>
+        <v>0.318</v>
       </c>
       <c r="I20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" s="1">
         <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>6</v>
-      </c>
-      <c r="L20" s="7">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <v>8</v>
+      </c>
+      <c r="L20" s="6">
+        <f t="shared" si="0"/>
+        <v>9.5</v>
       </c>
       <c r="M20" s="1">
-        <v>89</v>
+        <v>175</v>
       </c>
       <c r="N20" s="1">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="O20" s="1">
-        <v>12</v>
+        <v>-51</v>
       </c>
       <c r="P20" s="1"/>
     </row>
@@ -2082,145 +2160,145 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="1">
+        <v>18</v>
+      </c>
+      <c r="E21" s="1">
+        <v>8</v>
+      </c>
+      <c r="F21" s="1">
+        <v>3</v>
+      </c>
+      <c r="G21" s="1">
         <v>11</v>
       </c>
-      <c r="E21" s="1">
-        <v>5</v>
-      </c>
-      <c r="F21" s="1">
-        <v>5</v>
-      </c>
-      <c r="G21" s="1">
-        <v>10</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0.5</v>
+      <c r="H21" s="8">
+        <v>0.72699999999999998</v>
       </c>
       <c r="I21" s="1">
         <v>1</v>
       </c>
       <c r="J21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" s="1">
-        <v>8</v>
-      </c>
-      <c r="L21" s="7">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <v>2</v>
+      </c>
+      <c r="L21" s="10">
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="M21" s="1">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="N21" s="1">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="O21" s="1">
-        <v>-9</v>
+        <v>30</v>
       </c>
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="1">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E22" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1">
         <v>11</v>
       </c>
-      <c r="H22" s="2">
-        <v>0.36399999999999999</v>
+      <c r="H22" s="8">
+        <v>0.72699999999999998</v>
       </c>
       <c r="I22" s="1">
         <v>1</v>
       </c>
       <c r="J22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="1">
-        <v>8</v>
-      </c>
-      <c r="L22" s="7">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="L22" s="6">
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="M22" s="1">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="N22" s="1">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="O22" s="1">
-        <v>-19</v>
+        <v>25</v>
       </c>
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="1">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E23" s="1">
+        <v>6</v>
+      </c>
+      <c r="F23" s="1">
+        <v>4</v>
+      </c>
+      <c r="G23" s="1">
+        <v>10</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="I23" s="1">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1</v>
+      </c>
+      <c r="K23" s="1">
         <v>3</v>
       </c>
-      <c r="F23" s="1">
-        <v>6</v>
-      </c>
-      <c r="G23" s="1">
-        <v>9</v>
-      </c>
-      <c r="H23" s="2">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="I23" s="1">
-        <v>1</v>
-      </c>
-      <c r="J23" s="1">
-        <v>0</v>
-      </c>
-      <c r="K23" s="1">
-        <v>10</v>
-      </c>
-      <c r="L23" s="7">
-        <f t="shared" si="0"/>
-        <v>9</v>
+      <c r="L23" s="6">
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="M23" s="1">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="N23" s="1">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O23" s="1">
-        <v>-9</v>
+        <v>8</v>
       </c>
       <c r="P23" s="1"/>
     </row>
@@ -2229,25 +2307,25 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D24" s="1">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E24" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F24" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G24" s="1">
-        <v>10</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0.3</v>
+        <v>11</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0.63600000000000001</v>
       </c>
       <c r="I24" s="1">
         <v>1</v>
@@ -2256,47 +2334,47 @@
         <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>11</v>
-      </c>
-      <c r="L24" s="7">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="L24" s="6">
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="M24" s="1">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="N24" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="O24" s="1">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="1">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E25" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F25" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G25" s="1">
         <v>11</v>
       </c>
       <c r="H25" s="2">
-        <v>0.27300000000000002</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="I25" s="1">
         <v>1</v>
@@ -2305,47 +2383,47 @@
         <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>11</v>
-      </c>
-      <c r="L25" s="7">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="L25" s="6">
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="M25" s="1">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="N25" s="1">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="O25" s="1">
-        <v>-19</v>
+        <v>-1</v>
       </c>
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="D26" s="1">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E26" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F26" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G26" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H26" s="2">
-        <v>0.33300000000000002</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="I26" s="1">
         <v>1</v>
@@ -2354,20 +2432,20 @@
         <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>11</v>
-      </c>
-      <c r="L26" s="7">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="L26" s="6">
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="M26" s="1">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="N26" s="1">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O26" s="1">
-        <v>-18</v>
+        <v>13</v>
       </c>
       <c r="P26" s="1"/>
     </row>
@@ -2379,22 +2457,22 @@
         <v>37</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D27" s="1">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E27" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F27" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G27" s="1">
         <v>11</v>
       </c>
       <c r="H27" s="2">
-        <v>0.27300000000000002</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="I27" s="1">
         <v>1</v>
@@ -2403,22 +2481,365 @@
         <v>0</v>
       </c>
       <c r="K27" s="1">
+        <v>7</v>
+      </c>
+      <c r="L27" s="6">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="L27" s="7">
-        <f t="shared" si="0"/>
+      <c r="M27" s="1">
+        <v>96</v>
+      </c>
+      <c r="N27" s="1">
+        <v>110</v>
+      </c>
+      <c r="O27" s="1">
+        <v>-14</v>
+      </c>
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="1">
+        <v>11</v>
+      </c>
+      <c r="E28" s="1">
+        <v>5</v>
+      </c>
+      <c r="F28" s="1">
+        <v>5</v>
+      </c>
+      <c r="G28" s="1">
+        <v>10</v>
+      </c>
+      <c r="H28" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I28" s="1">
+        <v>1</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <v>8</v>
+      </c>
+      <c r="L28" s="6">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="M28" s="1">
+        <v>92</v>
+      </c>
+      <c r="N28" s="1">
+        <v>101</v>
+      </c>
+      <c r="O28" s="1">
+        <v>-9</v>
+      </c>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="1">
+        <v>9</v>
+      </c>
+      <c r="E29" s="1">
+        <v>3</v>
+      </c>
+      <c r="F29" s="1">
+        <v>6</v>
+      </c>
+      <c r="G29" s="1">
+        <v>9</v>
+      </c>
+      <c r="H29" s="2">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="I29" s="1">
+        <v>1</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <v>10</v>
+      </c>
+      <c r="L29" s="6">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="M29" s="1">
+        <v>87</v>
+      </c>
+      <c r="N29" s="1">
+        <v>96</v>
+      </c>
+      <c r="O29" s="1">
+        <v>-9</v>
+      </c>
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>27</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="1">
+        <v>9</v>
+      </c>
+      <c r="E30" s="1">
+        <v>3</v>
+      </c>
+      <c r="F30" s="1">
+        <v>8</v>
+      </c>
+      <c r="G30" s="1">
+        <v>11</v>
+      </c>
+      <c r="H30" s="2">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
+        <v>10</v>
+      </c>
+      <c r="L30" s="6">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="M30" s="1">
+        <v>95</v>
+      </c>
+      <c r="N30" s="1">
+        <v>114</v>
+      </c>
+      <c r="O30" s="1">
+        <v>-19</v>
+      </c>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>27</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="1">
+        <v>9</v>
+      </c>
+      <c r="E31" s="1">
+        <v>3</v>
+      </c>
+      <c r="F31" s="1">
+        <v>8</v>
+      </c>
+      <c r="G31" s="1">
+        <v>11</v>
+      </c>
+      <c r="H31" s="2">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="I31" s="1">
+        <v>1</v>
+      </c>
+      <c r="J31" s="1">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
+        <v>10</v>
+      </c>
+      <c r="L31" s="6">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="M31" s="1">
+        <v>92</v>
+      </c>
+      <c r="N31" s="1">
+        <v>112</v>
+      </c>
+      <c r="O31" s="1">
+        <v>-20</v>
+      </c>
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>30</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="1">
+        <v>8</v>
+      </c>
+      <c r="E32" s="1">
+        <v>3</v>
+      </c>
+      <c r="F32" s="1">
         <v>7</v>
       </c>
-      <c r="M27" s="1">
-        <v>84</v>
-      </c>
-      <c r="N27" s="1">
-        <v>115</v>
-      </c>
-      <c r="O27" s="1">
-        <v>-31</v>
-      </c>
-      <c r="P27" s="1"/>
+      <c r="G32" s="1">
+        <v>10</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="I32" s="1">
+        <v>1</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0</v>
+      </c>
+      <c r="K32" s="1">
+        <v>11</v>
+      </c>
+      <c r="L32" s="6">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="M32" s="1">
+        <v>99</v>
+      </c>
+      <c r="N32" s="1">
+        <v>100</v>
+      </c>
+      <c r="O32" s="1">
+        <v>-1</v>
+      </c>
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>30</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="1">
+        <v>8</v>
+      </c>
+      <c r="E33" s="1">
+        <v>3</v>
+      </c>
+      <c r="F33" s="1">
+        <v>8</v>
+      </c>
+      <c r="G33" s="1">
+        <v>11</v>
+      </c>
+      <c r="H33" s="2">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="I33" s="1">
+        <v>1</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0</v>
+      </c>
+      <c r="K33" s="1">
+        <v>11</v>
+      </c>
+      <c r="L33" s="6">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="M33" s="1">
+        <v>95</v>
+      </c>
+      <c r="N33" s="1">
+        <v>114</v>
+      </c>
+      <c r="O33" s="1">
+        <v>-19</v>
+      </c>
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>30</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="1">
+        <v>8</v>
+      </c>
+      <c r="E34" s="1">
+        <v>3</v>
+      </c>
+      <c r="F34" s="1">
+        <v>6</v>
+      </c>
+      <c r="G34" s="1">
+        <v>9</v>
+      </c>
+      <c r="H34" s="2">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1</v>
+      </c>
+      <c r="J34" s="1">
+        <v>0</v>
+      </c>
+      <c r="K34" s="1">
+        <v>11</v>
+      </c>
+      <c r="L34" s="6">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="M34" s="1">
+        <v>76</v>
+      </c>
+      <c r="N34" s="1">
+        <v>94</v>
+      </c>
+      <c r="O34" s="1">
+        <v>-18</v>
+      </c>
+      <c r="P34" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
